--- a/2026年度计划-九宫格.xlsx
+++ b/2026年度计划-九宫格.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>学习成长</t>
   </si>
@@ -83,6 +83,15 @@
     <t>家庭生活</t>
   </si>
   <si>
+    <t>评价</t>
+  </si>
+  <si>
+    <t>锻炼身体</t>
+  </si>
+  <si>
+    <t>亲子英语学习</t>
+  </si>
+  <si>
     <t>1、加密流量检测项目</t>
   </si>
   <si>
@@ -92,6 +101,9 @@
     <t>1、和圆圆一起蹲马步、打拳</t>
   </si>
   <si>
+    <t>做的好</t>
+  </si>
+  <si>
     <t>2、主机安全项目</t>
   </si>
   <si>
@@ -102,6 +114,12 @@
   </si>
   <si>
     <t>3、亲子学习英语(参加比赛)</t>
+  </si>
+  <si>
+    <t>有待加强</t>
+  </si>
+  <si>
+    <t>需加强</t>
   </si>
   <si>
     <t>身体健康</t>
@@ -345,7 +363,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,6 +384,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -409,12 +445,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -775,7 +805,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -799,16 +829,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -817,89 +847,89 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -936,6 +966,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -945,22 +978,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1294,7 +1330,9 @@
   <cols>
     <col min="1" max="7" width="9" style="1"/>
     <col min="8" max="8" width="14.125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="14" width="9" style="1"/>
+    <col min="15" max="15" width="15.5" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:18">
@@ -1472,30 +1510,42 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="11"/>
+      <c r="N8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" ht="20.25" spans="1:18">
       <c r="A9" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="14"/>
+      <c r="E9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="15"/>
       <c r="I9" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="8"/>
+      <c r="N9" s="16" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="10" ht="15.75" spans="1:18">
       <c r="A10" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1505,15 +1555,16 @@
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
       <c r="I10" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="8"/>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" ht="15.75" spans="1:18">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1523,11 +1574,17 @@
       <c r="G11" s="7"/>
       <c r="H11" s="8"/>
       <c r="I11" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="8"/>
+      <c r="N11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="12" ht="15.75" spans="1:18">
       <c r="A12" s="6"/>
@@ -1542,6 +1599,7 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="8"/>
+      <c r="N12" s="17"/>
     </row>
     <row r="13" ht="15.75" spans="1:18">
       <c r="A13" s="6"/>
@@ -1572,40 +1630,40 @@
       <c r="L14" s="8"/>
     </row>
     <row r="15" ht="16.5" spans="1:18">
-      <c r="A15" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="17"/>
+      <c r="A15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" ht="15.75" spans="1:18">
-      <c r="A16" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="21"/>
+      <c r="A16" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="23"/>
       <c r="I16" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -1613,19 +1671,19 @@
     </row>
     <row r="17" ht="15.75" spans="1:12">
       <c r="A17" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
       <c r="E17" s="6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="8"/>
       <c r="I17" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
@@ -1633,7 +1691,7 @@
     </row>
     <row r="18" ht="15.75" spans="1:12">
       <c r="A18" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1643,7 +1701,7 @@
       <c r="G18" s="7"/>
       <c r="H18" s="8"/>
       <c r="I18" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -1678,27 +1736,27 @@
       <c r="L20" s="8"/>
     </row>
     <row r="21" ht="15.75" spans="1:12">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="24"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="66">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="I1:L1"/>
@@ -1762,6 +1820,8 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:L21"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="N11:N12"/>
     <mergeCell ref="N1:R6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
